--- a/StructureDefinition-CWT.xlsx
+++ b/StructureDefinition-CWT.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T06:07:49+00:00</t>
+    <t>2023-11-14T21:40:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
